--- a/datasets/election_data/data/output/eu_statements.xlsx
+++ b/datasets/election_data/data/output/eu_statements.xlsx
@@ -754,7 +754,7 @@
         </is>
       </c>
       <c r="C25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
